--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="936" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF781593-FE96-4443-A5F3-3D5CD2D35A49}"/>
+  <xr:revisionPtr revIDLastSave="945" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{627AAA33-4E8E-47CE-8073-D72529F2F068}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="238">
   <si>
     <t>範疇</t>
   </si>
@@ -1015,6 +1015,18 @@
   </si>
   <si>
     <t>核銷總額</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>文具用品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>115/09/24</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1150902273</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2255,15 +2267,15 @@
       </c>
       <c r="D3" s="10">
         <f>SUMIF('明細表 '!B:B, B3, '明細表 '!D:D)</f>
-        <v>6068</v>
+        <v>6991</v>
       </c>
       <c r="E3" s="28">
         <f t="shared" ref="E3:E6" si="0">C3-D3</f>
-        <v>932</v>
+        <v>9</v>
       </c>
       <c r="F3" s="11">
         <f t="shared" ref="F3:F8" si="1">D3/C3</f>
-        <v>0.86685714285714288</v>
+        <v>0.99871428571428567</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1">
@@ -2366,15 +2378,15 @@
       </c>
       <c r="D8" s="9">
         <f>SUM(D2:D7)</f>
-        <v>149382</v>
+        <v>150305</v>
       </c>
       <c r="E8" s="28">
         <f>C8-D8</f>
-        <v>111818</v>
+        <v>110895</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="1"/>
-        <v>0.57190658499234304</v>
+        <v>0.57544027565084221</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
@@ -5170,17 +5182,35 @@
       <c r="K70" s="58"/>
     </row>
     <row r="71" spans="1:11">
-      <c r="A71" s="6"/>
-      <c r="B71" s="3"/>
-      <c r="C71" s="15"/>
-      <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
-      <c r="F71" s="2"/>
-      <c r="G71" s="2"/>
+      <c r="A71" s="6">
+        <v>46289</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="D71" s="2">
+        <v>923</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0</v>
+      </c>
+      <c r="F71" s="2">
+        <v>923</v>
+      </c>
+      <c r="G71" s="57" t="s">
+        <v>224</v>
+      </c>
       <c r="H71" s="15"/>
       <c r="I71" s="15"/>
-      <c r="J71" s="15"/>
-      <c r="K71" s="15"/>
+      <c r="J71" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="K71" s="15" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="72" spans="1:11">
       <c r="A72" s="6"/>

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="945" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{627AAA33-4E8E-47CE-8073-D72529F2F068}"/>
+  <xr:revisionPtr revIDLastSave="977" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F0F6D24-4E4D-40A0-886B-12E1812BD23E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="240">
   <si>
     <t>範疇</t>
   </si>
@@ -1027,6 +1027,14 @@
   </si>
   <si>
     <t>AE1150902273</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鄭雅靜副主任會議便當費(素食)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>小組會議便當(石蜜園)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2246,15 +2254,15 @@
       </c>
       <c r="D2" s="10">
         <f>SUMIF('明細表 '!B:B, B2, '明細表 '!D:D)</f>
-        <v>52758</v>
+        <v>57308</v>
       </c>
       <c r="E2" s="28">
         <f>C2-D2</f>
-        <v>77242</v>
+        <v>72692</v>
       </c>
       <c r="F2" s="11">
         <f>D2/C2</f>
-        <v>0.40583076923076922</v>
+        <v>0.44083076923076925</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
@@ -2342,7 +2350,7 @@
       </c>
       <c r="G6" s="22">
         <f>SUM(D5,D2)</f>
-        <v>72589</v>
+        <v>77139</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
@@ -2378,15 +2386,15 @@
       </c>
       <c r="D8" s="9">
         <f>SUM(D2:D7)</f>
-        <v>150305</v>
+        <v>154855</v>
       </c>
       <c r="E8" s="28">
         <f>C8-D8</f>
-        <v>110895</v>
+        <v>106345</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="1"/>
-        <v>0.57544027565084221</v>
+        <v>0.59285987748851454</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
@@ -2410,7 +2418,7 @@
       <c r="B10" s="86"/>
       <c r="C10" s="9">
         <f>SUMIF('明細表 '!B:B, "待沖帳", '明細表 '!D:D)</f>
-        <v>42013</v>
+        <v>46578</v>
       </c>
       <c r="D10" s="9">
         <f>SUM('明細表 '!E:E)</f>
@@ -2418,7 +2426,7 @@
       </c>
       <c r="E10" s="28">
         <f>(C10-D10)</f>
-        <v>2485</v>
+        <v>7050</v>
       </c>
       <c r="F10" s="11"/>
     </row>
@@ -2475,11 +2483,11 @@
       </c>
       <c r="E14" s="9">
         <f>E2+E5</f>
-        <v>77411</v>
+        <v>72861</v>
       </c>
       <c r="F14" s="23">
         <f>D14-E14</f>
-        <v>-12411</v>
+        <v>-7861</v>
       </c>
       <c r="G14" s="22"/>
     </row>
@@ -2625,7 +2633,7 @@
       </c>
       <c r="D24" s="9">
         <f>SUM(D2,D5)</f>
-        <v>72589</v>
+        <v>77139</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="17"/>
@@ -5213,12 +5221,24 @@
       </c>
     </row>
     <row r="72" spans="1:11">
-      <c r="A72" s="6"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="2"/>
-      <c r="E72" s="2"/>
-      <c r="F72" s="2"/>
+      <c r="A72" s="6">
+        <v>46301</v>
+      </c>
+      <c r="B72" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C72" s="16" t="s">
+        <v>238</v>
+      </c>
+      <c r="D72" s="2">
+        <v>140</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0</v>
+      </c>
+      <c r="F72" s="2">
+        <v>140</v>
+      </c>
       <c r="G72" s="2"/>
       <c r="H72" s="15"/>
       <c r="I72" s="15"/>
@@ -5226,12 +5246,24 @@
       <c r="K72" s="15"/>
     </row>
     <row r="73" spans="1:11">
-      <c r="A73" s="6"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="15"/>
-      <c r="D73" s="2"/>
-      <c r="E73" s="2"/>
-      <c r="F73" s="2"/>
+      <c r="A73" s="6">
+        <v>46301</v>
+      </c>
+      <c r="B73" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="D73" s="2">
+        <v>4550</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0</v>
+      </c>
+      <c r="F73" s="2">
+        <v>4550</v>
+      </c>
       <c r="G73" s="2"/>
       <c r="H73" s="15"/>
       <c r="I73" s="15"/>
@@ -5239,12 +5271,24 @@
       <c r="K73" s="15"/>
     </row>
     <row r="74" spans="1:11">
-      <c r="A74" s="6"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="15"/>
-      <c r="D74" s="2"/>
-      <c r="E74" s="2"/>
-      <c r="F74" s="2"/>
+      <c r="A74" s="6">
+        <v>46301</v>
+      </c>
+      <c r="B74" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C74" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="D74" s="2">
+        <v>4321</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0</v>
+      </c>
+      <c r="F74" s="2">
+        <v>4321</v>
+      </c>
       <c r="G74" s="2"/>
       <c r="H74" s="15"/>
       <c r="I74" s="15"/>
@@ -5252,12 +5296,24 @@
       <c r="K74" s="15"/>
     </row>
     <row r="75" spans="1:11">
-      <c r="A75" s="6"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="15"/>
-      <c r="D75" s="2"/>
-      <c r="E75" s="2"/>
-      <c r="F75" s="2"/>
+      <c r="A75" s="6">
+        <v>46301</v>
+      </c>
+      <c r="B75" s="56" t="s">
+        <v>192</v>
+      </c>
+      <c r="C75" s="58" t="s">
+        <v>223</v>
+      </c>
+      <c r="D75" s="2">
+        <v>104</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0</v>
+      </c>
+      <c r="F75" s="2">
+        <v>104</v>
+      </c>
       <c r="G75" s="2"/>
       <c r="H75" s="15"/>
       <c r="I75" s="15"/>

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="977" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F0F6D24-4E4D-40A0-886B-12E1812BD23E}"/>
+  <xr:revisionPtr revIDLastSave="983" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABE50349-4E3A-4D0A-9530-C10E4BA08DD1}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
     <sheet name="業務費總表" sheetId="1" r:id="rId2"/>
     <sheet name="明細表 " sheetId="10" r:id="rId3"/>
     <sheet name="業務費-租金" sheetId="7" r:id="rId4"/>
-    <sheet name="交通費" sheetId="4" r:id="rId5"/>
-    <sheet name="參數設定" sheetId="9" r:id="rId6"/>
+    <sheet name="業務費-人事費" sheetId="12" r:id="rId5"/>
+    <sheet name="交通費" sheetId="4" r:id="rId6"/>
+    <sheet name="參數設定" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'明細表 '!$A$1:$K$70</definedName>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="467" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="249">
   <si>
     <t>範疇</t>
   </si>
@@ -1035,6 +1036,36 @@
   </si>
   <si>
     <t>小組會議便當(石蜜園)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>業務費-人事費</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>研究助理3月薪資</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>研究助理4月薪資</t>
+  </si>
+  <si>
+    <t>研究助理5月薪資</t>
+  </si>
+  <si>
+    <t>研究助理6月薪資</t>
+  </si>
+  <si>
+    <t>研究助理7月薪資</t>
+  </si>
+  <si>
+    <t>研究助理8月薪資</t>
+  </si>
+  <si>
+    <t>研究助理9月薪資</t>
+  </si>
+  <si>
+    <t>研究助理6月三節獎金</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1387,7 +1418,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1608,6 +1639,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1974,7 +2008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E9FB1B8-A243-4826-9C79-80F20FB00855}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -1988,17 +2022,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="32" customFormat="1" ht="31.2" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="75" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:9" s="32" customFormat="1" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -2172,31 +2206,23 @@
       <c r="I8" s="15"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="76" t="s">
         <v>168</v>
       </c>
-      <c r="B9" s="76"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="77"/>
+      <c r="B9" s="77"/>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="78"/>
       <c r="F9" s="42">
         <f>SUM(F3:F8)</f>
         <v>3444000</v>
       </c>
-      <c r="G9" s="75"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="77"/>
+      <c r="G9" s="76"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="78"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="F12" s="46">
-        <f>SUM(F4:F6)</f>
-        <v>2856000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="F13">
-        <v>2856000</v>
-      </c>
+      <c r="F12" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -2243,7 +2269,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="84" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -2266,7 +2292,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A3" s="84"/>
+      <c r="A3" s="85"/>
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
@@ -2287,7 +2313,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A4" s="84"/>
+      <c r="A4" s="85"/>
       <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
@@ -2308,7 +2334,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="23.4">
-      <c r="A5" s="84"/>
+      <c r="A5" s="85"/>
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
@@ -2329,7 +2355,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A6" s="84"/>
+      <c r="A6" s="85"/>
       <c r="B6" s="8" t="s">
         <v>14</v>
       </c>
@@ -2354,7 +2380,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A7" s="85"/>
+      <c r="A7" s="86"/>
       <c r="B7" s="44" t="s">
         <v>174</v>
       </c>
@@ -2376,10 +2402,10 @@
       <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="79" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="79"/>
+      <c r="B8" s="80"/>
       <c r="C8" s="9">
         <f>SUM(C2:C7)</f>
         <v>261200</v>
@@ -2398,10 +2424,10 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="87" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="86"/>
+      <c r="B9" s="87"/>
       <c r="C9" s="71" t="s">
         <v>227</v>
       </c>
@@ -2414,8 +2440,8 @@
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="23.4">
-      <c r="A10" s="86"/>
-      <c r="B10" s="86"/>
+      <c r="A10" s="87"/>
+      <c r="B10" s="87"/>
       <c r="C10" s="9">
         <f>SUMIF('明細表 '!B:B, "待沖帳", '明細表 '!D:D)</f>
         <v>46578</v>
@@ -2439,7 +2465,7 @@
       <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A12" s="80"/>
+      <c r="A12" s="81"/>
       <c r="B12" s="12" t="s">
         <v>55</v>
       </c>
@@ -2457,7 +2483,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="31.2">
-      <c r="A13" s="81"/>
+      <c r="A13" s="82"/>
       <c r="B13" s="6" t="s">
         <v>21</v>
       </c>
@@ -2473,7 +2499,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="46.8">
-      <c r="A14" s="81"/>
+      <c r="A14" s="82"/>
       <c r="B14" s="6"/>
       <c r="C14" s="9" t="s">
         <v>41</v>
@@ -2492,7 +2518,7 @@
       <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:7" ht="46.8">
-      <c r="A15" s="81"/>
+      <c r="A15" s="82"/>
       <c r="B15" s="6">
         <v>46134</v>
       </c>
@@ -2508,7 +2534,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="46.8">
-      <c r="A16" s="82"/>
+      <c r="A16" s="83"/>
       <c r="B16" s="6">
         <v>46140</v>
       </c>
@@ -4430,10 +4456,10 @@
       <c r="G45" s="52"/>
       <c r="H45" s="24"/>
       <c r="I45" s="24"/>
-      <c r="J45" s="87" t="s">
+      <c r="J45" s="88" t="s">
         <v>117</v>
       </c>
-      <c r="K45" s="88" t="s">
+      <c r="K45" s="89" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4460,8 +4486,8 @@
       <c r="G46" s="52"/>
       <c r="H46" s="24"/>
       <c r="I46" s="24"/>
-      <c r="J46" s="87"/>
-      <c r="K46" s="88"/>
+      <c r="J46" s="88"/>
+      <c r="K46" s="89"/>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" s="55">
@@ -5674,17 +5700,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="75" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -5804,20 +5830,20 @@
       <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="76" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="77"/>
+      <c r="B8" s="77"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="78"/>
       <c r="F8" s="42">
         <f>SUM(F3:F7)</f>
         <v>371694</v>
       </c>
-      <c r="G8" s="75"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="77"/>
+      <c r="G8" s="76"/>
+      <c r="H8" s="77"/>
+      <c r="I8" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5832,6 +5858,186 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFB7564F-63EF-4B2B-8103-A3769055463C}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
+  <cols>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="75" t="s">
+        <v>240</v>
+      </c>
+      <c r="B1" s="75"/>
+      <c r="C1" s="75"/>
+      <c r="D1" s="75"/>
+      <c r="E1" s="75"/>
+      <c r="F1" s="75"/>
+    </row>
+    <row r="2" spans="1:6" ht="31.2">
+      <c r="A2" s="33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="E2" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="F2" s="34" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="36">
+        <v>46112</v>
+      </c>
+      <c r="B3" s="43" t="s">
+        <v>241</v>
+      </c>
+      <c r="C3" s="38">
+        <v>27231</v>
+      </c>
+      <c r="D3" s="37"/>
+      <c r="E3" s="43"/>
+      <c r="F3" s="37"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="36">
+        <v>46142</v>
+      </c>
+      <c r="B4" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="38">
+        <v>36893</v>
+      </c>
+      <c r="D4" s="37"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="15"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="36">
+        <v>46171</v>
+      </c>
+      <c r="B5" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="C5" s="38">
+        <v>37897</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="15"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="36">
+        <v>46203</v>
+      </c>
+      <c r="B6" s="43" t="s">
+        <v>244</v>
+      </c>
+      <c r="C6" s="38">
+        <v>37897</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="36">
+        <v>46203</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="38">
+        <v>4834</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="36">
+        <v>46234</v>
+      </c>
+      <c r="B8" s="43" t="s">
+        <v>245</v>
+      </c>
+      <c r="C8" s="38">
+        <v>37897</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15"/>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="36">
+        <v>46265</v>
+      </c>
+      <c r="B9" s="43" t="s">
+        <v>246</v>
+      </c>
+      <c r="C9" s="38">
+        <v>37897</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="36">
+        <v>46295</v>
+      </c>
+      <c r="B10" s="43" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="38">
+        <v>37897</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="76" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="77"/>
+      <c r="C11" s="42">
+        <f>SUM(C3:C10)</f>
+        <v>258443</v>
+      </c>
+      <c r="D11" s="76"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="78"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:F11"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FE949C4-C405-4DE6-96C8-B4016E88447D}">
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
@@ -5914,7 +6120,7 @@
         <v>131</v>
       </c>
       <c r="E4" s="29"/>
-      <c r="F4" s="89" t="s">
+      <c r="F4" s="90" t="s">
         <v>132</v>
       </c>
     </row>
@@ -5932,7 +6138,7 @@
         <v>131</v>
       </c>
       <c r="E5" s="29"/>
-      <c r="F5" s="89"/>
+      <c r="F5" s="90"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="30" t="s">
@@ -5962,7 +6168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FC0C220-C8EE-4B9E-8E82-2AF7148D585A}">
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="16.2"/>

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="983" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABE50349-4E3A-4D0A-9530-C10E4BA08DD1}"/>
+  <xr:revisionPtr revIDLastSave="1006" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE881B7F-9389-4AFF-A99C-7F2E0F68582D}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="253">
   <si>
     <t>範疇</t>
   </si>
@@ -1066,6 +1066,22 @@
   </si>
   <si>
     <t>研究助理6月三節獎金</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>還9/1田智蓉代墊款</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1151001696</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1151001693</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>115/10/07</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2280,15 +2296,15 @@
       </c>
       <c r="D2" s="10">
         <f>SUMIF('明細表 '!B:B, B2, '明細表 '!D:D)</f>
-        <v>57308</v>
+        <v>62838</v>
       </c>
       <c r="E2" s="28">
         <f>C2-D2</f>
-        <v>72692</v>
+        <v>67162</v>
       </c>
       <c r="F2" s="11">
         <f>D2/C2</f>
-        <v>0.44083076923076925</v>
+        <v>0.48336923076923077</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
@@ -2376,7 +2392,7 @@
       </c>
       <c r="G6" s="22">
         <f>SUM(D5,D2)</f>
-        <v>77139</v>
+        <v>82669</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
@@ -2412,15 +2428,15 @@
       </c>
       <c r="D8" s="9">
         <f>SUM(D2:D7)</f>
-        <v>154855</v>
+        <v>160385</v>
       </c>
       <c r="E8" s="28">
         <f>C8-D8</f>
-        <v>106345</v>
+        <v>100815</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="1"/>
-        <v>0.59285987748851454</v>
+        <v>0.61403139356814707</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
@@ -2444,15 +2460,15 @@
       <c r="B10" s="87"/>
       <c r="C10" s="9">
         <f>SUMIF('明細表 '!B:B, "待沖帳", '明細表 '!D:D)</f>
-        <v>46578</v>
+        <v>51128</v>
       </c>
       <c r="D10" s="9">
         <f>SUM('明細表 '!E:E)</f>
-        <v>39528</v>
+        <v>49608</v>
       </c>
       <c r="E10" s="28">
         <f>(C10-D10)</f>
-        <v>7050</v>
+        <v>1520</v>
       </c>
       <c r="F10" s="11"/>
     </row>
@@ -2509,11 +2525,11 @@
       </c>
       <c r="E14" s="9">
         <f>E2+E5</f>
-        <v>72861</v>
+        <v>67331</v>
       </c>
       <c r="F14" s="23">
         <f>D14-E14</f>
-        <v>-7861</v>
+        <v>-2331</v>
       </c>
       <c r="G14" s="22"/>
     </row>
@@ -2659,7 +2675,7 @@
       </c>
       <c r="D24" s="9">
         <f>SUM(D2,D5)</f>
-        <v>77139</v>
+        <v>82669</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="17"/>
@@ -5275,8 +5291,8 @@
       <c r="A73" s="6">
         <v>46301</v>
       </c>
-      <c r="B73" s="50" t="s">
-        <v>6</v>
+      <c r="B73" s="56" t="s">
+        <v>192</v>
       </c>
       <c r="C73" s="15" t="s">
         <v>239</v>
@@ -5347,12 +5363,24 @@
       <c r="K75" s="15"/>
     </row>
     <row r="76" spans="1:11">
-      <c r="A76" s="6"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="15"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
+      <c r="A76" s="6">
+        <v>46301</v>
+      </c>
+      <c r="B76" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="D76" s="2">
+        <v>1589</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0</v>
+      </c>
+      <c r="F76" s="2">
+        <v>1589</v>
+      </c>
       <c r="G76" s="2"/>
       <c r="H76" s="15"/>
       <c r="I76" s="15"/>
@@ -5360,30 +5388,62 @@
       <c r="K76" s="15"/>
     </row>
     <row r="77" spans="1:11">
-      <c r="A77" s="6"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="15"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
+      <c r="A77" s="6">
+        <v>46302</v>
+      </c>
+      <c r="B77" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="D77" s="2">
+        <v>5040</v>
+      </c>
+      <c r="E77" s="2">
+        <v>5040</v>
+      </c>
+      <c r="F77" s="2">
+        <v>0</v>
+      </c>
       <c r="G77" s="2"/>
       <c r="H77" s="15"/>
       <c r="I77" s="15"/>
-      <c r="J77" s="15"/>
-      <c r="K77" s="15"/>
+      <c r="J77" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="K77" s="15" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="78" spans="1:11">
-      <c r="A78" s="6"/>
-      <c r="B78" s="3"/>
-      <c r="C78" s="15"/>
-      <c r="D78" s="2"/>
-      <c r="E78" s="2"/>
-      <c r="F78" s="2"/>
+      <c r="A78" s="6">
+        <v>46302</v>
+      </c>
+      <c r="B78" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="D78" s="2">
+        <v>5040</v>
+      </c>
+      <c r="E78" s="2">
+        <v>5040</v>
+      </c>
+      <c r="F78" s="2">
+        <v>0</v>
+      </c>
       <c r="G78" s="2"/>
       <c r="H78" s="15"/>
       <c r="I78" s="15"/>
-      <c r="J78" s="15"/>
-      <c r="K78" s="15"/>
+      <c r="J78" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="K78" s="15" t="s">
+        <v>250</v>
+      </c>
     </row>
     <row r="79" spans="1:11">
       <c r="A79" s="6"/>

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1006" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE881B7F-9389-4AFF-A99C-7F2E0F68582D}"/>
+  <xr:revisionPtr revIDLastSave="1027" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91C8F727-4771-4614-A84F-CA0038D0B7A9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="493" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="258">
   <si>
     <t>範疇</t>
   </si>
@@ -1082,6 +1082,26 @@
   </si>
   <si>
     <t>115/10/07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FR24777851</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AI排班與加班預測系統採購案-第三階段(尾款)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>115/10/13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1151002157</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>第三階段</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1434,7 +1454,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="93">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1654,9 +1674,6 @@
     <xf numFmtId="3" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1707,6 +1724,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2031,24 +2057,24 @@
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.77734375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="32" customFormat="1" ht="31.2" customHeight="1">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="74" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
     </row>
     <row r="2" spans="1:9" s="32" customFormat="1" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -2083,7 +2109,7 @@
       <c r="A3" s="36">
         <v>46209</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="43" t="s">
         <v>143</v>
       </c>
       <c r="C3" s="37" t="s">
@@ -2092,10 +2118,10 @@
       <c r="D3" s="37">
         <v>1</v>
       </c>
-      <c r="E3" s="38">
+      <c r="E3" s="92">
         <v>588000</v>
       </c>
-      <c r="F3" s="38">
+      <c r="F3" s="92">
         <f>D3*E3</f>
         <v>588000</v>
       </c>
@@ -2113,7 +2139,7 @@
       <c r="A4" s="36">
         <v>46231</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="43" t="s">
         <v>153</v>
       </c>
       <c r="C4" s="15" t="s">
@@ -2122,20 +2148,20 @@
       <c r="D4" s="37">
         <v>1</v>
       </c>
-      <c r="E4" s="40">
+      <c r="E4" s="92">
         <v>1071000</v>
       </c>
-      <c r="F4" s="38">
-        <f t="shared" ref="F4:F6" si="0">D4*E4</f>
+      <c r="F4" s="92">
+        <f t="shared" ref="F4:F7" si="0">D4*E4</f>
         <v>1071000</v>
       </c>
       <c r="G4" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="H4" s="73" t="s">
+      <c r="H4" s="90" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="16" t="s">
+      <c r="I4" s="91" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2143,7 +2169,7 @@
       <c r="A5" s="36">
         <v>46231</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="43" t="s">
         <v>151</v>
       </c>
       <c r="C5" s="15" t="s">
@@ -2152,20 +2178,20 @@
       <c r="D5" s="37">
         <v>1</v>
       </c>
-      <c r="E5" s="40">
+      <c r="E5" s="92">
         <v>714000</v>
       </c>
-      <c r="F5" s="38">
+      <c r="F5" s="92">
         <f t="shared" si="0"/>
         <v>714000</v>
       </c>
       <c r="G5" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="H5" s="73" t="s">
+      <c r="H5" s="90" t="s">
         <v>149</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="37" t="s">
         <v>230</v>
       </c>
     </row>
@@ -2173,7 +2199,7 @@
       <c r="A6" s="36">
         <v>46231</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="43" t="s">
         <v>152</v>
       </c>
       <c r="C6" s="15" t="s">
@@ -2182,33 +2208,52 @@
       <c r="D6" s="37">
         <v>1</v>
       </c>
-      <c r="E6" s="40">
+      <c r="E6" s="92">
         <v>1071000</v>
       </c>
-      <c r="F6" s="38">
+      <c r="F6" s="92">
         <f t="shared" si="0"/>
         <v>1071000</v>
       </c>
       <c r="G6" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="73" t="s">
+      <c r="H6" s="90" t="s">
         <v>149</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="37" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="15"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
+      <c r="A7" s="36">
+        <v>46289</v>
+      </c>
+      <c r="B7" s="43" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>254</v>
+      </c>
+      <c r="D7" s="37">
+        <v>1</v>
+      </c>
+      <c r="E7" s="92">
+        <v>714000</v>
+      </c>
+      <c r="F7" s="92">
+        <f t="shared" si="0"/>
+        <v>714000</v>
+      </c>
+      <c r="G7" s="37" t="s">
+        <v>255</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="I7" s="37" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="15"/>
@@ -2222,20 +2267,20 @@
       <c r="I8" s="15"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="76" t="s">
+      <c r="A9" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="B9" s="77"/>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="78"/>
+      <c r="B9" s="76"/>
+      <c r="C9" s="76"/>
+      <c r="D9" s="76"/>
+      <c r="E9" s="77"/>
       <c r="F9" s="42">
         <f>SUM(F3:F8)</f>
-        <v>3444000</v>
-      </c>
-      <c r="G9" s="76"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="78"/>
+        <v>4158000</v>
+      </c>
+      <c r="G9" s="75"/>
+      <c r="H9" s="76"/>
+      <c r="I9" s="77"/>
     </row>
     <row r="12" spans="1:9">
       <c r="F12" s="46"/>
@@ -2285,7 +2330,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="83" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -2308,7 +2353,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A3" s="85"/>
+      <c r="A3" s="84"/>
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
@@ -2329,7 +2374,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A4" s="85"/>
+      <c r="A4" s="84"/>
       <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
@@ -2350,7 +2395,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="23.4">
-      <c r="A5" s="85"/>
+      <c r="A5" s="84"/>
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
@@ -2371,7 +2416,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A6" s="85"/>
+      <c r="A6" s="84"/>
       <c r="B6" s="8" t="s">
         <v>14</v>
       </c>
@@ -2396,7 +2441,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A7" s="86"/>
+      <c r="A7" s="85"/>
       <c r="B7" s="44" t="s">
         <v>174</v>
       </c>
@@ -2418,10 +2463,10 @@
       <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A8" s="79" t="s">
+      <c r="A8" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="80"/>
+      <c r="B8" s="79"/>
       <c r="C8" s="9">
         <f>SUM(C2:C7)</f>
         <v>261200</v>
@@ -2440,10 +2485,10 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
-      <c r="A9" s="87" t="s">
+      <c r="A9" s="86" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="87"/>
+      <c r="B9" s="86"/>
       <c r="C9" s="71" t="s">
         <v>227</v>
       </c>
@@ -2456,8 +2501,8 @@
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="23.4">
-      <c r="A10" s="87"/>
-      <c r="B10" s="87"/>
+      <c r="A10" s="86"/>
+      <c r="B10" s="86"/>
       <c r="C10" s="9">
         <f>SUMIF('明細表 '!B:B, "待沖帳", '明細表 '!D:D)</f>
         <v>51128</v>
@@ -2481,7 +2526,7 @@
       <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A12" s="81"/>
+      <c r="A12" s="80"/>
       <c r="B12" s="12" t="s">
         <v>55</v>
       </c>
@@ -2499,7 +2544,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="31.2">
-      <c r="A13" s="82"/>
+      <c r="A13" s="81"/>
       <c r="B13" s="6" t="s">
         <v>21</v>
       </c>
@@ -2515,7 +2560,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="46.8">
-      <c r="A14" s="82"/>
+      <c r="A14" s="81"/>
       <c r="B14" s="6"/>
       <c r="C14" s="9" t="s">
         <v>41</v>
@@ -2534,7 +2579,7 @@
       <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:7" ht="46.8">
-      <c r="A15" s="82"/>
+      <c r="A15" s="81"/>
       <c r="B15" s="6">
         <v>46134</v>
       </c>
@@ -2550,7 +2595,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="46.8">
-      <c r="A16" s="83"/>
+      <c r="A16" s="82"/>
       <c r="B16" s="6">
         <v>46140</v>
       </c>
@@ -4472,10 +4517,10 @@
       <c r="G45" s="52"/>
       <c r="H45" s="24"/>
       <c r="I45" s="24"/>
-      <c r="J45" s="88" t="s">
+      <c r="J45" s="87" t="s">
         <v>117</v>
       </c>
-      <c r="K45" s="89" t="s">
+      <c r="K45" s="88" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4502,8 +4547,8 @@
       <c r="G46" s="52"/>
       <c r="H46" s="24"/>
       <c r="I46" s="24"/>
-      <c r="J46" s="88"/>
-      <c r="K46" s="89"/>
+      <c r="J46" s="87"/>
+      <c r="K46" s="88"/>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" s="55">
@@ -5760,17 +5805,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="74" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
-      <c r="G1" s="75"/>
-      <c r="H1" s="75"/>
-      <c r="I1" s="75"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -5890,20 +5935,20 @@
       <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="76" t="s">
+      <c r="A8" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="77"/>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="78"/>
+      <c r="B8" s="76"/>
+      <c r="C8" s="76"/>
+      <c r="D8" s="76"/>
+      <c r="E8" s="77"/>
       <c r="F8" s="42">
         <f>SUM(F3:F7)</f>
         <v>371694</v>
       </c>
-      <c r="G8" s="76"/>
-      <c r="H8" s="77"/>
-      <c r="I8" s="78"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="76"/>
+      <c r="I8" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5931,14 +5976,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="74" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75"/>
-      <c r="D1" s="75"/>
-      <c r="E1" s="75"/>
-      <c r="F1" s="75"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
     </row>
     <row r="2" spans="1:6" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -5985,7 +6030,7 @@
         <v>36893</v>
       </c>
       <c r="D4" s="37"/>
-      <c r="E4" s="74"/>
+      <c r="E4" s="73"/>
       <c r="F4" s="15"/>
     </row>
     <row r="5" spans="1:6">
@@ -5999,7 +6044,7 @@
         <v>37897</v>
       </c>
       <c r="D5" s="37"/>
-      <c r="E5" s="74"/>
+      <c r="E5" s="73"/>
       <c r="F5" s="15"/>
     </row>
     <row r="6" spans="1:6">
@@ -6073,17 +6118,17 @@
       <c r="F10" s="15"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="76" t="s">
+      <c r="A11" s="75" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="77"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="42">
         <f>SUM(C3:C10)</f>
         <v>258443</v>
       </c>
-      <c r="D11" s="76"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="78"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="76"/>
+      <c r="F11" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6180,7 +6225,7 @@
         <v>131</v>
       </c>
       <c r="E4" s="29"/>
-      <c r="F4" s="90" t="s">
+      <c r="F4" s="89" t="s">
         <v>132</v>
       </c>
     </row>
@@ -6198,7 +6243,7 @@
         <v>131</v>
       </c>
       <c r="E5" s="29"/>
-      <c r="F5" s="90"/>
+      <c r="F5" s="89"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="30" t="s">

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -1677,6 +1677,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1724,15 +1733,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2064,17 +2064,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="32" customFormat="1" ht="31.2" customHeight="1">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="77" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" s="32" customFormat="1" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -2118,10 +2118,10 @@
       <c r="D3" s="37">
         <v>1</v>
       </c>
-      <c r="E3" s="92">
+      <c r="E3" s="76">
         <v>588000</v>
       </c>
-      <c r="F3" s="92">
+      <c r="F3" s="76">
         <f>D3*E3</f>
         <v>588000</v>
       </c>
@@ -2148,20 +2148,20 @@
       <c r="D4" s="37">
         <v>1</v>
       </c>
-      <c r="E4" s="92">
+      <c r="E4" s="76">
         <v>1071000</v>
       </c>
-      <c r="F4" s="92">
+      <c r="F4" s="76">
         <f t="shared" ref="F4:F7" si="0">D4*E4</f>
         <v>1071000</v>
       </c>
       <c r="G4" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="H4" s="90" t="s">
+      <c r="H4" s="74" t="s">
         <v>149</v>
       </c>
-      <c r="I4" s="91" t="s">
+      <c r="I4" s="75" t="s">
         <v>229</v>
       </c>
     </row>
@@ -2178,17 +2178,17 @@
       <c r="D5" s="37">
         <v>1</v>
       </c>
-      <c r="E5" s="92">
+      <c r="E5" s="76">
         <v>714000</v>
       </c>
-      <c r="F5" s="92">
+      <c r="F5" s="76">
         <f t="shared" si="0"/>
         <v>714000</v>
       </c>
       <c r="G5" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="H5" s="90" t="s">
+      <c r="H5" s="74" t="s">
         <v>149</v>
       </c>
       <c r="I5" s="37" t="s">
@@ -2208,17 +2208,17 @@
       <c r="D6" s="37">
         <v>1</v>
       </c>
-      <c r="E6" s="92">
+      <c r="E6" s="76">
         <v>1071000</v>
       </c>
-      <c r="F6" s="92">
+      <c r="F6" s="76">
         <f t="shared" si="0"/>
         <v>1071000</v>
       </c>
       <c r="G6" s="37" t="s">
         <v>150</v>
       </c>
-      <c r="H6" s="90" t="s">
+      <c r="H6" s="74" t="s">
         <v>149</v>
       </c>
       <c r="I6" s="37" t="s">
@@ -2238,10 +2238,10 @@
       <c r="D7" s="37">
         <v>1</v>
       </c>
-      <c r="E7" s="92">
+      <c r="E7" s="76">
         <v>714000</v>
       </c>
-      <c r="F7" s="92">
+      <c r="F7" s="76">
         <f t="shared" si="0"/>
         <v>714000</v>
       </c>
@@ -2267,20 +2267,20 @@
       <c r="I8" s="15"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="75" t="s">
+      <c r="A9" s="78" t="s">
         <v>168</v>
       </c>
-      <c r="B9" s="76"/>
-      <c r="C9" s="76"/>
-      <c r="D9" s="76"/>
-      <c r="E9" s="77"/>
+      <c r="B9" s="79"/>
+      <c r="C9" s="79"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="80"/>
       <c r="F9" s="42">
         <f>SUM(F3:F8)</f>
         <v>4158000</v>
       </c>
-      <c r="G9" s="75"/>
-      <c r="H9" s="76"/>
-      <c r="I9" s="77"/>
+      <c r="G9" s="78"/>
+      <c r="H9" s="79"/>
+      <c r="I9" s="80"/>
     </row>
     <row r="12" spans="1:9">
       <c r="F12" s="46"/>
@@ -2330,7 +2330,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A2" s="83" t="s">
+      <c r="A2" s="86" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -2353,7 +2353,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A3" s="84"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
@@ -2374,7 +2374,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A4" s="84"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
@@ -2395,7 +2395,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="23.4">
-      <c r="A5" s="84"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
@@ -2416,7 +2416,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A6" s="84"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="8" t="s">
         <v>14</v>
       </c>
@@ -2441,7 +2441,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A7" s="85"/>
+      <c r="A7" s="88"/>
       <c r="B7" s="44" t="s">
         <v>174</v>
       </c>
@@ -2463,10 +2463,10 @@
       <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="79"/>
+      <c r="B8" s="82"/>
       <c r="C8" s="9">
         <f>SUM(C2:C7)</f>
         <v>261200</v>
@@ -2485,10 +2485,10 @@
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
-      <c r="A9" s="86" t="s">
+      <c r="A9" s="89" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="86"/>
+      <c r="B9" s="89"/>
       <c r="C9" s="71" t="s">
         <v>227</v>
       </c>
@@ -2501,8 +2501,8 @@
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="23.4">
-      <c r="A10" s="86"/>
-      <c r="B10" s="86"/>
+      <c r="A10" s="89"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="9">
         <f>SUMIF('明細表 '!B:B, "待沖帳", '明細表 '!D:D)</f>
         <v>51128</v>
@@ -2526,7 +2526,7 @@
       <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A12" s="80"/>
+      <c r="A12" s="83"/>
       <c r="B12" s="12" t="s">
         <v>55</v>
       </c>
@@ -2544,7 +2544,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="31.2">
-      <c r="A13" s="81"/>
+      <c r="A13" s="84"/>
       <c r="B13" s="6" t="s">
         <v>21</v>
       </c>
@@ -2560,7 +2560,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="46.8">
-      <c r="A14" s="81"/>
+      <c r="A14" s="84"/>
       <c r="B14" s="6"/>
       <c r="C14" s="9" t="s">
         <v>41</v>
@@ -2579,7 +2579,7 @@
       <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:7" ht="46.8">
-      <c r="A15" s="81"/>
+      <c r="A15" s="84"/>
       <c r="B15" s="6">
         <v>46134</v>
       </c>
@@ -2595,7 +2595,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="46.8">
-      <c r="A16" s="82"/>
+      <c r="A16" s="85"/>
       <c r="B16" s="6">
         <v>46140</v>
       </c>
@@ -4517,10 +4517,10 @@
       <c r="G45" s="52"/>
       <c r="H45" s="24"/>
       <c r="I45" s="24"/>
-      <c r="J45" s="87" t="s">
+      <c r="J45" s="90" t="s">
         <v>117</v>
       </c>
-      <c r="K45" s="88" t="s">
+      <c r="K45" s="91" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4547,8 +4547,8 @@
       <c r="G46" s="52"/>
       <c r="H46" s="24"/>
       <c r="I46" s="24"/>
-      <c r="J46" s="87"/>
-      <c r="K46" s="88"/>
+      <c r="J46" s="90"/>
+      <c r="K46" s="91"/>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" s="55">
@@ -5805,17 +5805,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="77" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
-      <c r="G1" s="74"/>
-      <c r="H1" s="74"/>
-      <c r="I1" s="74"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
+      <c r="G1" s="77"/>
+      <c r="H1" s="77"/>
+      <c r="I1" s="77"/>
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -5935,20 +5935,20 @@
       <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="75" t="s">
+      <c r="A8" s="78" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="76"/>
-      <c r="C8" s="76"/>
-      <c r="D8" s="76"/>
-      <c r="E8" s="77"/>
+      <c r="B8" s="79"/>
+      <c r="C8" s="79"/>
+      <c r="D8" s="79"/>
+      <c r="E8" s="80"/>
       <c r="F8" s="42">
         <f>SUM(F3:F7)</f>
         <v>371694</v>
       </c>
-      <c r="G8" s="75"/>
-      <c r="H8" s="76"/>
-      <c r="I8" s="77"/>
+      <c r="G8" s="78"/>
+      <c r="H8" s="79"/>
+      <c r="I8" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5976,14 +5976,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="77" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="74"/>
-      <c r="D1" s="74"/>
-      <c r="E1" s="74"/>
-      <c r="F1" s="74"/>
+      <c r="B1" s="77"/>
+      <c r="C1" s="77"/>
+      <c r="D1" s="77"/>
+      <c r="E1" s="77"/>
+      <c r="F1" s="77"/>
     </row>
     <row r="2" spans="1:6" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -6118,17 +6118,17 @@
       <c r="F10" s="15"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="75" t="s">
+      <c r="A11" s="78" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="76"/>
+      <c r="B11" s="79"/>
       <c r="C11" s="42">
         <f>SUM(C3:C10)</f>
         <v>258443</v>
       </c>
-      <c r="D11" s="75"/>
-      <c r="E11" s="76"/>
-      <c r="F11" s="77"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="79"/>
+      <c r="F11" s="80"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6225,7 +6225,7 @@
         <v>131</v>
       </c>
       <c r="E4" s="29"/>
-      <c r="F4" s="89" t="s">
+      <c r="F4" s="92" t="s">
         <v>132</v>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
         <v>131</v>
       </c>
       <c r="E5" s="29"/>
-      <c r="F5" s="89"/>
+      <c r="F5" s="92"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="30" t="s">

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1027" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91C8F727-4771-4614-A84F-CA0038D0B7A9}"/>
+  <xr:revisionPtr revIDLastSave="1032" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2A95397-9CD7-427F-A303-485B814D1093}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="259">
   <si>
     <t>範疇</t>
   </si>
@@ -1102,6 +1102,10 @@
   </si>
   <si>
     <t>第三階段</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>還資材蔡宛臻</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -5491,12 +5495,20 @@
       </c>
     </row>
     <row r="79" spans="1:11">
-      <c r="A79" s="6"/>
-      <c r="B79" s="3"/>
-      <c r="C79" s="15"/>
+      <c r="A79" s="6">
+        <v>46315</v>
+      </c>
+      <c r="B79" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C79" s="15" t="s">
+        <v>258</v>
+      </c>
       <c r="D79" s="2"/>
       <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
+      <c r="F79" s="2">
+        <v>1772</v>
+      </c>
       <c r="G79" s="2"/>
       <c r="H79" s="15"/>
       <c r="I79" s="15"/>

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1032" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2A95397-9CD7-427F-A303-485B814D1093}"/>
+  <xr:revisionPtr revIDLastSave="1060" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{864AFC98-13BA-42FF-ADBB-F3259FBC8229}"/>
   <bookViews>
     <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="269">
   <si>
     <t>範疇</t>
   </si>
@@ -1106,6 +1106,46 @@
   </si>
   <si>
     <t>還資材蔡宛臻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>餐費</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ERP系統會議</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>導入數位病理系統會議</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1151003589</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>115/10/29</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1151003595</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資材室餐費</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡宛臻</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>病理部餐費</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蔡佳蓉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2059,7 +2099,7 @@
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="12.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.77734375" bestFit="1" customWidth="1"/>
@@ -2116,7 +2156,7 @@
       <c r="B3" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="43" t="s">
         <v>145</v>
       </c>
       <c r="D3" s="37">
@@ -2146,7 +2186,7 @@
       <c r="B4" s="43" t="s">
         <v>153</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="43" t="s">
         <v>154</v>
       </c>
       <c r="D4" s="37">
@@ -2176,7 +2216,7 @@
       <c r="B5" s="43" t="s">
         <v>151</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="43" t="s">
         <v>155</v>
       </c>
       <c r="D5" s="37">
@@ -2206,7 +2246,7 @@
       <c r="B6" s="43" t="s">
         <v>152</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="43" t="s">
         <v>156</v>
       </c>
       <c r="D6" s="37">
@@ -2236,7 +2276,7 @@
       <c r="B7" s="43" t="s">
         <v>253</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="C7" s="43" t="s">
         <v>254</v>
       </c>
       <c r="D7" s="37">
@@ -2345,15 +2385,15 @@
       </c>
       <c r="D2" s="10">
         <f>SUMIF('明細表 '!B:B, B2, '明細表 '!D:D)</f>
-        <v>62838</v>
+        <v>67318</v>
       </c>
       <c r="E2" s="28">
         <f>C2-D2</f>
-        <v>67162</v>
+        <v>62682</v>
       </c>
       <c r="F2" s="11">
         <f>D2/C2</f>
-        <v>0.48336923076923077</v>
+        <v>0.51783076923076921</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
@@ -2441,7 +2481,7 @@
       </c>
       <c r="G6" s="22">
         <f>SUM(D5,D2)</f>
-        <v>82669</v>
+        <v>87149</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
@@ -2477,15 +2517,15 @@
       </c>
       <c r="D8" s="9">
         <f>SUM(D2:D7)</f>
-        <v>160385</v>
+        <v>164865</v>
       </c>
       <c r="E8" s="28">
         <f>C8-D8</f>
-        <v>100815</v>
+        <v>96335</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="1"/>
-        <v>0.61403139356814707</v>
+        <v>0.63118300153139362</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
@@ -2513,11 +2553,11 @@
       </c>
       <c r="D10" s="9">
         <f>SUM('明細表 '!E:E)</f>
-        <v>49608</v>
+        <v>50088</v>
       </c>
       <c r="E10" s="28">
         <f>(C10-D10)</f>
-        <v>1520</v>
+        <v>1040</v>
       </c>
       <c r="F10" s="11"/>
     </row>
@@ -2574,11 +2614,11 @@
       </c>
       <c r="E14" s="9">
         <f>E2+E5</f>
-        <v>67331</v>
+        <v>62851</v>
       </c>
       <c r="F14" s="23">
         <f>D14-E14</f>
-        <v>-2331</v>
+        <v>2149</v>
       </c>
       <c r="G14" s="22"/>
     </row>
@@ -2724,7 +2764,7 @@
       </c>
       <c r="D24" s="9">
         <f>SUM(D2,D5)</f>
-        <v>82669</v>
+        <v>87149</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="17"/>
@@ -5516,52 +5556,100 @@
       <c r="K79" s="15"/>
     </row>
     <row r="80" spans="1:11">
-      <c r="A80" s="6"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="15"/>
+      <c r="A80" s="6">
+        <v>46316</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C80" s="15" t="s">
+        <v>260</v>
+      </c>
       <c r="D80" s="2"/>
       <c r="E80" s="2"/>
-      <c r="F80" s="2"/>
+      <c r="F80" s="2">
+        <v>2100</v>
+      </c>
       <c r="G80" s="2"/>
       <c r="H80" s="15"/>
       <c r="I80" s="15"/>
-      <c r="J80" s="15"/>
-      <c r="K80" s="15"/>
+      <c r="J80" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="K80" s="15" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="81" spans="1:11">
-      <c r="A81" s="6"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="15"/>
-      <c r="D81" s="2"/>
-      <c r="E81" s="2"/>
-      <c r="F81" s="2"/>
+      <c r="A81" s="6">
+        <v>46315</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C81" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="D81" s="2">
+        <v>4480</v>
+      </c>
+      <c r="E81" s="2">
+        <v>480</v>
+      </c>
+      <c r="F81" s="2">
+        <v>4000</v>
+      </c>
       <c r="G81" s="2"/>
       <c r="H81" s="15"/>
       <c r="I81" s="15"/>
-      <c r="J81" s="15"/>
-      <c r="K81" s="15"/>
+      <c r="J81" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="K81" s="15" t="s">
+        <v>262</v>
+      </c>
     </row>
     <row r="82" spans="1:11">
-      <c r="A82" s="6"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="15"/>
+      <c r="A82" s="6">
+        <v>46323</v>
+      </c>
+      <c r="B82" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C82" s="15" t="s">
+        <v>265</v>
+      </c>
       <c r="D82" s="2"/>
       <c r="E82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
+      <c r="F82" s="2">
+        <v>2100</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>266</v>
+      </c>
       <c r="H82" s="15"/>
       <c r="I82" s="15"/>
       <c r="J82" s="15"/>
       <c r="K82" s="15"/>
     </row>
     <row r="83" spans="1:11">
-      <c r="A83" s="6"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="15"/>
+      <c r="A83" s="6">
+        <v>46324</v>
+      </c>
+      <c r="B83" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C83" s="15" t="s">
+        <v>267</v>
+      </c>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
+      <c r="F83" s="2">
+        <v>4000</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>268</v>
+      </c>
       <c r="H83" s="15"/>
       <c r="I83" s="15"/>
       <c r="J83" s="15"/>

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1060" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{864AFC98-13BA-42FF-ADBB-F3259FBC8229}"/>
+  <xr:revisionPtr revIDLastSave="1078" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DF296C6-D000-4964-9E02-5B4D7BE371BF}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="275">
   <si>
     <t>範疇</t>
   </si>
@@ -1146,6 +1146,30 @@
   </si>
   <si>
     <t>蔡佳蓉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FP73185466</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>9月租金-手術智慧排程與管理系統</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1151004460</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10月租金-手術智慧排程與管理系統</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>FP73185491</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1151004487</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1498,7 +1522,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1776,6 +1800,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -5894,7 +5921,7 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="42.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
@@ -6002,25 +6029,59 @@
       <c r="I4" s="15"/>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="36"/>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="40"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="37"/>
-      <c r="H5" s="41"/>
+      <c r="A5" s="36">
+        <v>46286</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>270</v>
+      </c>
+      <c r="D5" s="37">
+        <v>1</v>
+      </c>
+      <c r="E5" s="40">
+        <v>349167</v>
+      </c>
+      <c r="F5" s="38">
+        <f>E5*D5</f>
+        <v>349167</v>
+      </c>
+      <c r="G5" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="H5" s="41" t="s">
+        <v>271</v>
+      </c>
       <c r="I5" s="15"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="15"/>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
+      <c r="A6" s="93">
+        <v>46315</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>272</v>
+      </c>
+      <c r="D6" s="37">
+        <v>1</v>
+      </c>
+      <c r="E6" s="40">
+        <v>349167</v>
+      </c>
+      <c r="F6" s="38">
+        <f>E6*D6</f>
+        <v>349167</v>
+      </c>
+      <c r="G6" s="37" t="s">
+        <v>263</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>274</v>
+      </c>
       <c r="I6" s="15"/>
     </row>
     <row r="7" spans="1:9">
@@ -6044,7 +6105,7 @@
       <c r="E8" s="80"/>
       <c r="F8" s="42">
         <f>SUM(F3:F7)</f>
-        <v>371694</v>
+        <v>1070028</v>
       </c>
       <c r="G8" s="78"/>
       <c r="H8" s="79"/>

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1078" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DF296C6-D000-4964-9E02-5B4D7BE371BF}"/>
+  <xr:revisionPtr revIDLastSave="1113" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DE48C5-7CC0-4A7B-BDD8-AB7A4F401499}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="284">
   <si>
     <t>範疇</t>
   </si>
@@ -1170,6 +1170,37 @@
   </si>
   <si>
     <t>AE1151004487</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>職安室餐費</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>林佳瑩</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>職安室項目討論</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AE1151004606</t>
+  </si>
+  <si>
+    <t>AE1151004599</t>
+  </si>
+  <si>
+    <t>AE1151004601</t>
+  </si>
+  <si>
+    <t>AE1151004602</t>
+  </si>
+  <si>
+    <t>AE1151004603</t>
+  </si>
+  <si>
+    <t>115/10/30</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1754,6 +1785,9 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="17" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -1800,9 +1834,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2135,17 +2166,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="32" customFormat="1" ht="31.2" customHeight="1">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" s="32" customFormat="1" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -2338,20 +2369,20 @@
       <c r="I8" s="15"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="78" t="s">
+      <c r="A9" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="B9" s="79"/>
-      <c r="C9" s="79"/>
-      <c r="D9" s="79"/>
-      <c r="E9" s="80"/>
+      <c r="B9" s="80"/>
+      <c r="C9" s="80"/>
+      <c r="D9" s="80"/>
+      <c r="E9" s="81"/>
       <c r="F9" s="42">
         <f>SUM(F3:F8)</f>
         <v>4158000</v>
       </c>
-      <c r="G9" s="78"/>
-      <c r="H9" s="79"/>
-      <c r="I9" s="80"/>
+      <c r="G9" s="79"/>
+      <c r="H9" s="80"/>
+      <c r="I9" s="81"/>
     </row>
     <row r="12" spans="1:9">
       <c r="F12" s="46"/>
@@ -2401,7 +2432,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="87" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -2412,19 +2443,19 @@
       </c>
       <c r="D2" s="10">
         <f>SUMIF('明細表 '!B:B, B2, '明細表 '!D:D)</f>
-        <v>67318</v>
+        <v>76668</v>
       </c>
       <c r="E2" s="28">
         <f>C2-D2</f>
-        <v>62682</v>
+        <v>53332</v>
       </c>
       <c r="F2" s="11">
         <f>D2/C2</f>
-        <v>0.51783076923076921</v>
+        <v>0.58975384615384618</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A3" s="87"/>
+      <c r="A3" s="88"/>
       <c r="B3" s="8" t="s">
         <v>7</v>
       </c>
@@ -2445,7 +2476,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A4" s="87"/>
+      <c r="A4" s="88"/>
       <c r="B4" s="8" t="s">
         <v>8</v>
       </c>
@@ -2466,7 +2497,7 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="23.4">
-      <c r="A5" s="87"/>
+      <c r="A5" s="88"/>
       <c r="B5" s="8" t="s">
         <v>9</v>
       </c>
@@ -2487,7 +2518,7 @@
       </c>
     </row>
     <row r="6" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A6" s="87"/>
+      <c r="A6" s="88"/>
       <c r="B6" s="8" t="s">
         <v>14</v>
       </c>
@@ -2508,11 +2539,11 @@
       </c>
       <c r="G6" s="22">
         <f>SUM(D5,D2)</f>
-        <v>87149</v>
+        <v>96499</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A7" s="88"/>
+      <c r="A7" s="89"/>
       <c r="B7" s="44" t="s">
         <v>174</v>
       </c>
@@ -2534,32 +2565,32 @@
       <c r="G7" s="22"/>
     </row>
     <row r="8" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A8" s="81" t="s">
+      <c r="A8" s="82" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="82"/>
+      <c r="B8" s="83"/>
       <c r="C8" s="9">
         <f>SUM(C2:C7)</f>
         <v>261200</v>
       </c>
       <c r="D8" s="9">
         <f>SUM(D2:D7)</f>
-        <v>164865</v>
+        <v>174215</v>
       </c>
       <c r="E8" s="28">
         <f>C8-D8</f>
-        <v>96335</v>
+        <v>86985</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="1"/>
-        <v>0.63118300153139362</v>
+        <v>0.66697932618682998</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
-      <c r="A9" s="89" t="s">
+      <c r="A9" s="90" t="s">
         <v>228</v>
       </c>
-      <c r="B9" s="89"/>
+      <c r="B9" s="90"/>
       <c r="C9" s="71" t="s">
         <v>227</v>
       </c>
@@ -2572,19 +2603,19 @@
       <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:7" ht="23.4">
-      <c r="A10" s="89"/>
-      <c r="B10" s="89"/>
+      <c r="A10" s="90"/>
+      <c r="B10" s="90"/>
       <c r="C10" s="9">
         <f>SUMIF('明細表 '!B:B, "待沖帳", '明細表 '!D:D)</f>
         <v>51128</v>
       </c>
       <c r="D10" s="9">
         <f>SUM('明細表 '!E:E)</f>
-        <v>50088</v>
+        <v>51388</v>
       </c>
       <c r="E10" s="28">
         <f>(C10-D10)</f>
-        <v>1040</v>
+        <v>-260</v>
       </c>
       <c r="F10" s="11"/>
     </row>
@@ -2597,7 +2628,7 @@
       <c r="F11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="19.95" customHeight="1">
-      <c r="A12" s="83"/>
+      <c r="A12" s="84"/>
       <c r="B12" s="12" t="s">
         <v>55</v>
       </c>
@@ -2615,7 +2646,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" ht="31.2">
-      <c r="A13" s="84"/>
+      <c r="A13" s="85"/>
       <c r="B13" s="6" t="s">
         <v>21</v>
       </c>
@@ -2631,7 +2662,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="46.8">
-      <c r="A14" s="84"/>
+      <c r="A14" s="85"/>
       <c r="B14" s="6"/>
       <c r="C14" s="9" t="s">
         <v>41</v>
@@ -2641,16 +2672,16 @@
       </c>
       <c r="E14" s="9">
         <f>E2+E5</f>
-        <v>62851</v>
+        <v>53501</v>
       </c>
       <c r="F14" s="23">
         <f>D14-E14</f>
-        <v>2149</v>
+        <v>11499</v>
       </c>
       <c r="G14" s="22"/>
     </row>
     <row r="15" spans="1:7" ht="46.8">
-      <c r="A15" s="84"/>
+      <c r="A15" s="85"/>
       <c r="B15" s="6">
         <v>46134</v>
       </c>
@@ -2666,7 +2697,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="46.8">
-      <c r="A16" s="85"/>
+      <c r="A16" s="86"/>
       <c r="B16" s="6">
         <v>46140</v>
       </c>
@@ -2791,7 +2822,7 @@
       </c>
       <c r="D24" s="9">
         <f>SUM(D2,D5)</f>
-        <v>87149</v>
+        <v>96499</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="17"/>
@@ -4588,10 +4619,10 @@
       <c r="G45" s="52"/>
       <c r="H45" s="24"/>
       <c r="I45" s="24"/>
-      <c r="J45" s="90" t="s">
+      <c r="J45" s="91" t="s">
         <v>117</v>
       </c>
-      <c r="K45" s="91" t="s">
+      <c r="K45" s="92" t="s">
         <v>116</v>
       </c>
     </row>
@@ -4618,8 +4649,8 @@
       <c r="G46" s="52"/>
       <c r="H46" s="24"/>
       <c r="I46" s="24"/>
-      <c r="J46" s="90"/>
-      <c r="K46" s="91"/>
+      <c r="J46" s="91"/>
+      <c r="K46" s="92"/>
     </row>
     <row r="47" spans="1:20">
       <c r="A47" s="55">
@@ -5683,95 +5714,207 @@
       <c r="K83" s="15"/>
     </row>
     <row r="84" spans="1:11">
-      <c r="A84" s="6"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="15"/>
+      <c r="A84" s="6">
+        <v>46325</v>
+      </c>
+      <c r="B84" s="56" t="s">
+        <v>209</v>
+      </c>
+      <c r="C84" s="15" t="s">
+        <v>275</v>
+      </c>
       <c r="D84" s="2"/>
       <c r="E84" s="2"/>
-      <c r="F84" s="2"/>
-      <c r="G84" s="2"/>
+      <c r="F84" s="2">
+        <v>8000</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>276</v>
+      </c>
       <c r="H84" s="15"/>
       <c r="I84" s="15"/>
       <c r="J84" s="15"/>
       <c r="K84" s="15"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="6"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="15"/>
-      <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
+      <c r="A85" s="6">
+        <v>46296</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C85" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D85" s="2">
+        <v>1680</v>
+      </c>
+      <c r="E85" s="2">
+        <f>D85-F85</f>
+        <v>0</v>
+      </c>
+      <c r="F85" s="2">
+        <v>1680</v>
+      </c>
       <c r="G85" s="2"/>
       <c r="H85" s="15"/>
       <c r="I85" s="15"/>
-      <c r="J85" s="15"/>
-      <c r="K85" s="15"/>
+      <c r="J85" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K85" s="15" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="86" spans="1:11">
-      <c r="A86" s="6"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="15"/>
-      <c r="D86" s="2"/>
-      <c r="E86" s="2"/>
-      <c r="F86" s="2"/>
+      <c r="A86" s="6">
+        <v>46302</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C86" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D86" s="2">
+        <v>1290</v>
+      </c>
+      <c r="E86" s="2">
+        <f>D86-F86</f>
+        <v>0</v>
+      </c>
+      <c r="F86" s="2">
+        <v>1290</v>
+      </c>
       <c r="G86" s="2"/>
       <c r="H86" s="15"/>
       <c r="I86" s="15"/>
-      <c r="J86" s="15"/>
-      <c r="K86" s="15"/>
+      <c r="J86" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K86" s="15" t="s">
+        <v>279</v>
+      </c>
     </row>
     <row r="87" spans="1:11">
-      <c r="A87" s="6"/>
-      <c r="B87" s="3"/>
-      <c r="C87" s="15"/>
-      <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
+      <c r="A87" s="6">
+        <v>46308</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C87" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D87" s="2">
+        <v>1540</v>
+      </c>
+      <c r="E87" s="2">
+        <f>D87-F87</f>
+        <v>550</v>
+      </c>
+      <c r="F87" s="2">
+        <v>990</v>
+      </c>
       <c r="G87" s="2"/>
       <c r="H87" s="15"/>
       <c r="I87" s="15"/>
-      <c r="J87" s="15"/>
-      <c r="K87" s="15"/>
+      <c r="J87" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K87" s="15" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="88" spans="1:11">
-      <c r="A88" s="6"/>
-      <c r="B88" s="3"/>
-      <c r="C88" s="15"/>
-      <c r="D88" s="2"/>
-      <c r="E88" s="2"/>
-      <c r="F88" s="2"/>
+      <c r="A88" s="6">
+        <v>46309</v>
+      </c>
+      <c r="B88" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C88" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D88" s="2">
+        <v>1540</v>
+      </c>
+      <c r="E88" s="2">
+        <f>D88-F88</f>
+        <v>520</v>
+      </c>
+      <c r="F88" s="2">
+        <v>1020</v>
+      </c>
       <c r="G88" s="2"/>
       <c r="H88" s="15"/>
       <c r="I88" s="15"/>
-      <c r="J88" s="15"/>
-      <c r="K88" s="15"/>
+      <c r="J88" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K88" s="15" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="89" spans="1:11">
-      <c r="A89" s="6"/>
-      <c r="B89" s="3"/>
-      <c r="C89" s="15"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
+      <c r="A89" s="6">
+        <v>46316</v>
+      </c>
+      <c r="B89" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D89" s="2">
+        <v>1620</v>
+      </c>
+      <c r="E89" s="2">
+        <f>D89-F89</f>
+        <v>0</v>
+      </c>
+      <c r="F89" s="2">
+        <v>1620</v>
+      </c>
       <c r="G89" s="2"/>
       <c r="H89" s="15"/>
       <c r="I89" s="15"/>
-      <c r="J89" s="15"/>
-      <c r="K89" s="15"/>
+      <c r="J89" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K89" s="15" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="90" spans="1:11">
-      <c r="A90" s="6"/>
-      <c r="B90" s="3"/>
-      <c r="C90" s="15"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
+      <c r="A90" s="6">
+        <v>46322</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="C90" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="D90" s="2">
+        <v>1680</v>
+      </c>
+      <c r="E90" s="2">
+        <f>D90-F90</f>
+        <v>230</v>
+      </c>
+      <c r="F90" s="2">
+        <v>1450</v>
+      </c>
       <c r="G90" s="2"/>
       <c r="H90" s="15"/>
       <c r="I90" s="15"/>
-      <c r="J90" s="15"/>
-      <c r="K90" s="15"/>
+      <c r="J90" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K90" s="15" t="s">
+        <v>278</v>
+      </c>
     </row>
     <row r="91" spans="1:11">
       <c r="A91" s="6"/>
@@ -5932,17 +6075,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
-      <c r="G1" s="77"/>
-      <c r="H1" s="77"/>
-      <c r="I1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
     </row>
     <row r="2" spans="1:9" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -6057,7 +6200,7 @@
       <c r="I5" s="15"/>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="93">
+      <c r="A6" s="77">
         <v>46315</v>
       </c>
       <c r="B6" s="15" t="s">
@@ -6096,20 +6239,20 @@
       <c r="I7" s="15"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="B8" s="79"/>
-      <c r="C8" s="79"/>
-      <c r="D8" s="79"/>
-      <c r="E8" s="80"/>
+      <c r="B8" s="80"/>
+      <c r="C8" s="80"/>
+      <c r="D8" s="80"/>
+      <c r="E8" s="81"/>
       <c r="F8" s="42">
         <f>SUM(F3:F7)</f>
         <v>1070028</v>
       </c>
-      <c r="G8" s="78"/>
-      <c r="H8" s="79"/>
-      <c r="I8" s="80"/>
+      <c r="G8" s="79"/>
+      <c r="H8" s="80"/>
+      <c r="I8" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6137,14 +6280,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="78" t="s">
         <v>240</v>
       </c>
-      <c r="B1" s="77"/>
-      <c r="C1" s="77"/>
-      <c r="D1" s="77"/>
-      <c r="E1" s="77"/>
-      <c r="F1" s="77"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
     </row>
     <row r="2" spans="1:6" ht="31.2">
       <c r="A2" s="33" t="s">
@@ -6279,17 +6422,17 @@
       <c r="F10" s="15"/>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="78" t="s">
+      <c r="A11" s="79" t="s">
         <v>168</v>
       </c>
-      <c r="B11" s="79"/>
+      <c r="B11" s="80"/>
       <c r="C11" s="42">
         <f>SUM(C3:C10)</f>
         <v>258443</v>
       </c>
-      <c r="D11" s="78"/>
-      <c r="E11" s="79"/>
-      <c r="F11" s="80"/>
+      <c r="D11" s="79"/>
+      <c r="E11" s="80"/>
+      <c r="F11" s="81"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6386,7 +6529,7 @@
         <v>131</v>
       </c>
       <c r="E4" s="29"/>
-      <c r="F4" s="92" t="s">
+      <c r="F4" s="93" t="s">
         <v>132</v>
       </c>
     </row>
@@ -6404,7 +6547,7 @@
         <v>131</v>
       </c>
       <c r="E5" s="29"/>
-      <c r="F5" s="92"/>
+      <c r="F5" s="93"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="30" t="s">

--- a/114~115年度_範疇一經費支用紀錄明細.xlsx
+++ b/114~115年度_範疇一經費支用紀錄明細.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailcmuhorgtw-my.sharepoint.com/personal/033951_tool_caaumed_org_tw/Documents/CMUH/健康台灣深耕計畫/115年費用核銷/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1113" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63DE48C5-7CC0-4A7B-BDD8-AB7A4F401499}"/>
+  <xr:revisionPtr revIDLastSave="1115" documentId="13_ncr:1_{182D9DB2-ED36-4605-9D4B-D74488644F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3D52249-1E1A-402E-B371-A402C9A6CDC1}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{9CC1BB25-7D3B-4ECC-A3A2-A5AB657F9242}"/>
   </bookViews>
   <sheets>
     <sheet name="資本門" sheetId="6" r:id="rId1"/>
@@ -22,7 +22,7 @@
     <sheet name="參數設定" sheetId="9" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'明細表 '!$A$1:$K$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'明細表 '!$A$1:$K$90</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2443,15 +2443,15 @@
       </c>
       <c r="D2" s="10">
         <f>SUMIF('明細表 '!B:B, B2, '明細表 '!D:D)</f>
-        <v>76668</v>
+        <v>78768</v>
       </c>
       <c r="E2" s="28">
         <f>C2-D2</f>
-        <v>53332</v>
+        <v>51232</v>
       </c>
       <c r="F2" s="11">
         <f>D2/C2</f>
-        <v>0.58975384615384618</v>
+        <v>0.60590769230769226</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19.95" customHeight="1">
@@ -2539,7 +2539,7 @@
       </c>
       <c r="G6" s="22">
         <f>SUM(D5,D2)</f>
-        <v>96499</v>
+        <v>98599</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="19.95" customHeight="1">
@@ -2575,15 +2575,15 @@
       </c>
       <c r="D8" s="9">
         <f>SUM(D2:D7)</f>
-        <v>174215</v>
+        <v>176315</v>
       </c>
       <c r="E8" s="28">
         <f>C8-D8</f>
-        <v>86985</v>
+        <v>84885</v>
       </c>
       <c r="F8" s="11">
         <f t="shared" si="1"/>
-        <v>0.66697932618682998</v>
+        <v>0.67501914241960181</v>
       </c>
     </row>
     <row r="9" spans="1:7" ht="23.4" customHeight="1">
@@ -2672,11 +2672,11 @@
       </c>
       <c r="E14" s="9">
         <f>E2+E5</f>
-        <v>53501</v>
+        <v>51401</v>
       </c>
       <c r="F14" s="23">
         <f>D14-E14</f>
-        <v>11499</v>
+        <v>13599</v>
       </c>
       <c r="G14" s="22"/>
     </row>
@@ -2822,7 +2822,7 @@
       </c>
       <c r="D24" s="9">
         <f>SUM(D2,D5)</f>
-        <v>96499</v>
+        <v>98599</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="17"/>
@@ -3112,7 +3112,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D507EA38-39D7-4602-A1BB-B46B528661DB}">
-  <sheetPr>
+  <sheetPr filterMode="1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:T100"/>
@@ -3173,7 +3173,7 @@
       <c r="S1"/>
       <c r="T1"/>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:20" hidden="1">
       <c r="A2" s="49">
         <v>46058</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:20">
+    <row r="5" spans="1:20" hidden="1">
       <c r="A5" s="53">
         <v>46106</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:20">
+    <row r="6" spans="1:20" hidden="1">
       <c r="A6" s="53">
         <v>46107</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:20">
+    <row r="7" spans="1:20" hidden="1">
       <c r="A7" s="53">
         <v>46107</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:20">
+    <row r="9" spans="1:20" hidden="1">
       <c r="A9" s="53">
         <v>46111</v>
       </c>
@@ -3445,7 +3445,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:20">
+    <row r="10" spans="1:20" hidden="1">
       <c r="A10" s="55">
         <v>46120</v>
       </c>
@@ -3471,7 +3471,7 @@
       <c r="J10" s="58"/>
       <c r="K10" s="58"/>
     </row>
-    <row r="11" spans="1:20">
+    <row r="11" spans="1:20" hidden="1">
       <c r="A11" s="53">
         <v>46121</v>
       </c>
@@ -3537,7 +3537,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="15" customHeight="1">
+    <row r="13" spans="1:20" ht="15" hidden="1" customHeight="1">
       <c r="A13" s="53">
         <v>46126</v>
       </c>
@@ -3567,7 +3567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:20">
+    <row r="14" spans="1:20" hidden="1">
       <c r="A14" s="53">
         <v>46126</v>
       </c>
@@ -3603,7 +3603,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:20">
+    <row r="15" spans="1:20" hidden="1">
       <c r="A15" s="53">
         <v>46134</v>
       </c>
@@ -3637,7 +3637,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="32.4">
+    <row r="16" spans="1:20" ht="32.4" hidden="1">
       <c r="A16" s="53">
         <v>46135</v>
       </c>
@@ -3674,7 +3674,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="32.4">
+    <row r="17" spans="1:20" ht="32.4" hidden="1">
       <c r="A17" s="53">
         <v>46135</v>
       </c>
@@ -3708,7 +3708,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="18" spans="1:20">
+    <row r="18" spans="1:20" hidden="1">
       <c r="A18" s="53">
         <v>46135</v>
       </c>
@@ -3742,7 +3742,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="19" spans="1:20">
+    <row r="19" spans="1:20" hidden="1">
       <c r="A19" s="53">
         <v>46133</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="20" spans="1:20">
+    <row r="20" spans="1:20" hidden="1">
       <c r="A20" s="53">
         <v>46135</v>
       </c>
@@ -3806,7 +3806,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="21" spans="1:20">
+    <row r="21" spans="1:20" hidden="1">
       <c r="A21" s="53">
         <v>46136</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="22" spans="1:20">
+    <row r="22" spans="1:20" hidden="1">
       <c r="A22" s="53">
         <v>46141</v>
       </c>
@@ -3872,7 +3872,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="23" spans="1:20">
+    <row r="23" spans="1:20" hidden="1">
       <c r="A23" s="53">
         <v>46142</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="24" spans="1:20">
+    <row r="24" spans="1:20" hidden="1">
       <c r="A24" s="53">
         <v>46142</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="32.4">
+    <row r="25" spans="1:20" ht="32.4" hidden="1">
       <c r="A25" s="53">
         <v>46134</v>
       </c>
@@ -3972,7 +3972,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="32.4">
+    <row r="26" spans="1:20" ht="32.4" hidden="1">
       <c r="A26" s="53">
         <v>46136</v>
       </c>
@@ -4004,7 +4004,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="27" spans="1:20" ht="32.4" customHeight="1">
+    <row r="27" spans="1:20" ht="32.4" hidden="1" customHeight="1">
       <c r="A27" s="53">
         <v>46141</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:20" ht="32.4">
+    <row r="28" spans="1:20" ht="32.4" hidden="1">
       <c r="A28" s="53">
         <v>46141</v>
       </c>
@@ -4066,7 +4066,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="29" spans="1:20" ht="32.4">
+    <row r="29" spans="1:20" ht="32.4" hidden="1">
       <c r="A29" s="53">
         <v>46146</v>
       </c>
@@ -4098,7 +4098,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="30" spans="1:20" s="25" customFormat="1">
+    <row r="30" spans="1:20" s="25" customFormat="1" hidden="1">
       <c r="A30" s="55">
         <v>46157</v>
       </c>
@@ -4201,7 +4201,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="33" spans="1:20" s="27" customFormat="1">
+    <row r="33" spans="1:20" s="27" customFormat="1" hidden="1">
       <c r="A33" s="55">
         <v>46163</v>
       </c>
@@ -4236,7 +4236,7 @@
       <c r="S33"/>
       <c r="T33"/>
     </row>
-    <row r="34" spans="1:20">
+    <row r="34" spans="1:20" hidden="1">
       <c r="A34" s="55">
         <v>46164</v>
       </c>
@@ -4270,7 +4270,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="35" spans="1:20" s="27" customFormat="1">
+    <row r="35" spans="1:20" s="27" customFormat="1" hidden="1">
       <c r="A35" s="55">
         <v>46164</v>
       </c>
@@ -4305,7 +4305,7 @@
       <c r="S35"/>
       <c r="T35"/>
     </row>
-    <row r="36" spans="1:20" ht="32.4">
+    <row r="36" spans="1:20" ht="32.4" hidden="1">
       <c r="A36" s="53">
         <v>46164</v>
       </c>
@@ -4339,7 +4339,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="37" spans="1:20">
+    <row r="37" spans="1:20" hidden="1">
       <c r="A37" s="53">
         <v>46167</v>
       </c>
@@ -4367,7 +4367,7 @@
       <c r="J37" s="24"/>
       <c r="K37" s="24"/>
     </row>
-    <row r="38" spans="1:20">
+    <row r="38" spans="1:20" hidden="1">
       <c r="A38" s="53">
         <v>46167</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="J38" s="24"/>
       <c r="K38" s="24"/>
     </row>
-    <row r="39" spans="1:20">
+    <row r="39" spans="1:20" hidden="1">
       <c r="A39" s="53">
         <v>46168</v>
       </c>
@@ -4423,7 +4423,7 @@
       <c r="J39" s="24"/>
       <c r="K39" s="24"/>
     </row>
-    <row r="40" spans="1:20" s="27" customFormat="1">
+    <row r="40" spans="1:20" s="27" customFormat="1" hidden="1">
       <c r="A40" s="55">
         <v>46169</v>
       </c>
@@ -4462,7 +4462,7 @@
       <c r="S40"/>
       <c r="T40"/>
     </row>
-    <row r="41" spans="1:20" s="27" customFormat="1">
+    <row r="41" spans="1:20" s="27" customFormat="1" hidden="1">
       <c r="A41" s="55">
         <v>46169</v>
       </c>
@@ -4501,7 +4501,7 @@
       <c r="S41"/>
       <c r="T41"/>
     </row>
-    <row r="42" spans="1:20" s="27" customFormat="1">
+    <row r="42" spans="1:20" s="27" customFormat="1" hidden="1">
       <c r="A42" s="55">
         <v>46169</v>
       </c>
@@ -4596,7 +4596,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="45" spans="1:20">
+    <row r="45" spans="1:20" hidden="1">
       <c r="A45" s="53">
         <v>46181</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:20">
+    <row r="46" spans="1:20" hidden="1">
       <c r="A46" s="53">
         <v>46181</v>
       </c>
@@ -4652,7 +4652,7 @@
       <c r="J46" s="91"/>
       <c r="K46" s="92"/>
     </row>
-    <row r="47" spans="1:20">
+    <row r="47" spans="1:20" hidden="1">
       <c r="A47" s="55">
         <v>46184</v>
       </c>
@@ -4682,7 +4682,7 @@
       <c r="J47" s="58"/>
       <c r="K47" s="58"/>
     </row>
-    <row r="48" spans="1:20">
+    <row r="48" spans="1:20" hidden="1">
       <c r="A48" s="55">
         <v>46210</v>
       </c>
@@ -4710,7 +4710,7 @@
       <c r="J48" s="58"/>
       <c r="K48" s="58"/>
     </row>
-    <row r="49" spans="1:11" ht="64.8">
+    <row r="49" spans="1:11" ht="64.8" hidden="1">
       <c r="A49" s="55">
         <v>46184</v>
       </c>
@@ -4740,7 +4740,7 @@
       <c r="J49" s="58"/>
       <c r="K49" s="58"/>
     </row>
-    <row r="50" spans="1:11" ht="32.4">
+    <row r="50" spans="1:11" ht="32.4" hidden="1">
       <c r="A50" s="53">
         <v>46184</v>
       </c>
@@ -4774,7 +4774,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="32.4">
+    <row r="51" spans="1:11" ht="32.4" hidden="1">
       <c r="A51" s="53">
         <v>46184</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="54" spans="1:11" s="69" customFormat="1">
+    <row r="54" spans="1:11" s="69" customFormat="1" hidden="1">
       <c r="A54" s="55">
         <v>46188</v>
       </c>
@@ -4922,7 +4922,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="56" spans="1:11" s="69" customFormat="1">
+    <row r="56" spans="1:11" s="69" customFormat="1" hidden="1">
       <c r="A56" s="55">
         <v>46197</v>
       </c>
@@ -5008,7 +5008,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="59" spans="1:11" s="69" customFormat="1">
+    <row r="59" spans="1:11" s="69" customFormat="1" hidden="1">
       <c r="A59" s="55">
         <v>46231</v>
       </c>
@@ -5094,7 +5094,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="48.6">
+    <row r="62" spans="1:11" ht="48.6" hidden="1">
       <c r="A62" s="53">
         <v>46240</v>
       </c>
@@ -5156,7 +5156,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="32.4">
+    <row r="64" spans="1:11" ht="32.4" hidden="1">
       <c r="A64" s="53">
         <v>46107</v>
       </c>
@@ -5190,7 +5190,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="32.4">
+    <row r="65" spans="1:11" ht="32.4" hidden="1">
       <c r="A65" s="53">
         <v>46184</v>
       </c>
@@ -5224,7 +5224,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="32.4">
+    <row r="66" spans="1:11" ht="32.4" hidden="1">
       <c r="A66" s="53">
         <v>46185</v>
       </c>
@@ -5322,7 +5322,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="69" spans="1:11" s="69" customFormat="1">
+    <row r="69" spans="1:11" s="69" customFormat="1" hidden="1">
       <c r="A69" s="55">
         <v>46266</v>
       </c>
@@ -5350,7 +5350,7 @@
       <c r="J69" s="58"/>
       <c r="K69" s="58"/>
     </row>
-    <row r="70" spans="1:11" s="69" customFormat="1">
+    <row r="70" spans="1:11" s="69" customFormat="1" hidden="1">
       <c r="A70" s="55">
         <v>46266</v>
       </c>
@@ -5378,7 +5378,7 @@
       <c r="J70" s="58"/>
       <c r="K70" s="58"/>
     </row>
-    <row r="71" spans="1:11">
+    <row r="71" spans="1:11" hidden="1">
       <c r="A71" s="6">
         <v>46289</v>
       </c>
@@ -5409,7 +5409,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="72" spans="1:11">
+    <row r="72" spans="1:11" hidden="1">
       <c r="A72" s="6">
         <v>46301</v>
       </c>
@@ -5434,7 +5434,7 @@
       <c r="J72" s="15"/>
       <c r="K72" s="15"/>
     </row>
-    <row r="73" spans="1:11">
+    <row r="73" spans="1:11" hidden="1">
       <c r="A73" s="6">
         <v>46301</v>
       </c>
@@ -5459,7 +5459,7 @@
       <c r="J73" s="15"/>
       <c r="K73" s="15"/>
     </row>
-    <row r="74" spans="1:11">
+    <row r="74" spans="1:11" hidden="1">
       <c r="A74" s="6">
         <v>46301</v>
       </c>
@@ -5484,7 +5484,7 @@
       <c r="J74" s="15"/>
       <c r="K74" s="15"/>
     </row>
-    <row r="75" spans="1:11">
+    <row r="75" spans="1:11" hidden="1">
       <c r="A75" s="6">
         <v>46301</v>
       </c>
@@ -5509,7 +5509,7 @@
       <c r="J75" s="15"/>
       <c r="K75" s="15"/>
     </row>
-    <row r="76" spans="1:11">
+    <row r="76" spans="1:11" hidden="1">
       <c r="A76" s="6">
         <v>46301</v>
       </c>
@@ -5592,7 +5592,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="79" spans="1:11">
+    <row r="79" spans="1:11" hidden="1">
       <c r="A79" s="6">
         <v>46315</v>
       </c>
@@ -5623,7 +5623,9 @@
       <c r="C80" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="D80" s="2"/>
+      <c r="D80" s="2">
+        <v>2100</v>
+      </c>
       <c r="E80" s="2"/>
       <c r="F80" s="2">
         <v>2100</v>
@@ -5667,7 +5669,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="82" spans="1:11">
+    <row r="82" spans="1:11" hidden="1">
       <c r="A82" s="6">
         <v>46323</v>
       </c>
@@ -5690,7 +5692,7 @@
       <c r="J82" s="15"/>
       <c r="K82" s="15"/>
     </row>
-    <row r="83" spans="1:11">
+    <row r="83" spans="1:11" hidden="1">
       <c r="A83" s="6">
         <v>46324</v>
       </c>
@@ -5713,7 +5715,7 @@
       <c r="J83" s="15"/>
       <c r="K83" s="15"/>
     </row>
-    <row r="84" spans="1:11">
+    <row r="84" spans="1:11" hidden="1">
       <c r="A84" s="6">
         <v>46325</v>
       </c>
@@ -5750,7 +5752,7 @@
         <v>1680</v>
       </c>
       <c r="E85" s="2">
-        <f>D85-F85</f>
+        <f t="shared" ref="E85:E90" si="2">D85-F85</f>
         <v>0</v>
       </c>
       <c r="F85" s="2">
@@ -5780,7 +5782,7 @@
         <v>1290</v>
       </c>
       <c r="E86" s="2">
-        <f>D86-F86</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F86" s="2">
@@ -5810,7 +5812,7 @@
         <v>1540</v>
       </c>
       <c r="E87" s="2">
-        <f>D87-F87</f>
+        <f t="shared" si="2"/>
         <v>550</v>
       </c>
       <c r="F87" s="2">
@@ -5840,7 +5842,7 @@
         <v>1540</v>
       </c>
       <c r="E88" s="2">
-        <f>D88-F88</f>
+        <f t="shared" si="2"/>
         <v>520</v>
       </c>
       <c r="F88" s="2">
@@ -5870,7 +5872,7 @@
         <v>1620</v>
       </c>
       <c r="E89" s="2">
-        <f>D89-F89</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="F89" s="2">
@@ -5900,7 +5902,7 @@
         <v>1680</v>
       </c>
       <c r="E90" s="2">
-        <f>D90-F90</f>
+        <f t="shared" si="2"/>
         <v>230</v>
       </c>
       <c r="F90" s="2">
@@ -6047,7 +6049,13 @@
       <c r="K100" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K70" xr:uid="{BC203A93-8841-4BBB-9060-EA16340AF533}"/>
+  <autoFilter ref="A1:K90" xr:uid="{BC203A93-8841-4BBB-9060-EA16340AF533}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="餐費"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataConsolidate/>
   <mergeCells count="2">
     <mergeCell ref="J45:J46"/>
